--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,49 +680,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80876638</v>
+        <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>98050</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222112</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Labbgård-Stocklunda Z767, Jmt</t>
+          <t>Labbgård, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502438</v>
+        <v>502749</v>
       </c>
       <c r="R2" t="n">
-        <v>7028128</v>
+        <v>7028075</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,18 +767,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Sara Lundkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -784,38 +789,38 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80876638</t>
+          <t>https://artportalen.se/Sighting/136949694</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80876640</v>
+        <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>98050</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222112</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -823,16 +828,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Labbgård-Stocklunda Z767, Jmt</t>
+          <t>Labbgård, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502240</v>
+        <v>502295</v>
       </c>
       <c r="R3" t="n">
-        <v>7028156</v>
+        <v>7028133</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -859,12 +868,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,18 +882,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Sara Lundkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -894,55 +904,59 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80876640</t>
+          <t>https://artportalen.se/Sighting/136949696</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80876641</v>
+        <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>98050</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222112</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Labbgård-Stocklunda Z767, Jmt</t>
+          <t>Labbgård, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502249</v>
+        <v>501997</v>
       </c>
       <c r="R4" t="n">
-        <v>7028155</v>
+        <v>7028293</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,12 +983,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,18 +997,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Signe Jönsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1004,55 +1019,59 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80876641</t>
+          <t>https://artportalen.se/Sighting/136950119</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80876642</v>
+        <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>98050</v>
+        <v>99377</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222112</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Labbgård-Stocklunda Z767, Jmt</t>
+          <t>Labbgård, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502235</v>
+        <v>502761</v>
       </c>
       <c r="R5" t="n">
-        <v>7028164</v>
+        <v>7028065</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,12 +1098,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,18 +1112,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Signe Jönsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1114,55 +1134,59 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80876642</t>
+          <t>https://artportalen.se/Sighting/136950117</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80876643</v>
+        <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>98050</v>
+        <v>99377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222112</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Labbgård-Stocklunda Z767, Jmt</t>
+          <t>Labbgård, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502234</v>
+        <v>502368</v>
       </c>
       <c r="R6" t="n">
-        <v>7028151</v>
+        <v>7028127</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,12 +1213,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,18 +1227,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Signe Jönsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1224,13 +1249,13 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80876643</t>
+          <t>https://artportalen.se/Sighting/136950118</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80876644</v>
+        <v>80876638</v>
       </c>
       <c r="B7" t="n">
         <v>98050</v>
@@ -1260,7 +1285,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1269,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501943</v>
+        <v>502438</v>
       </c>
       <c r="R7" t="n">
-        <v>7028328</v>
+        <v>7028128</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1359,672 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/80876638</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>80876640</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Labbgård-Stocklunda Z767, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>502240</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7028156</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80876640</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>80876641</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Labbgård-Stocklunda Z767, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>502249</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7028155</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80876641</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>80876642</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Labbgård-Stocklunda Z767, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>502235</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7028164</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80876642</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>80876643</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Labbgård-Stocklunda Z767, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>502234</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7028151</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80876643</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>80876644</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Labbgård-Stocklunda Z767, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>501943</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7028328</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/80876644</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136949695</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98282</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Labbgård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>502248</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7028147</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136949695</t>
         </is>
       </c>
     </row>
@@ -1346,6 +2036,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98282</v>
+        <v>98288</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98288</v>
+        <v>98290</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98291</v>
+        <v>98297</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98297</v>
+        <v>98301</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98301</v>
+        <v>98303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98303</v>
+        <v>98305</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98305</v>
+        <v>98318</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98318</v>
+        <v>98320</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98320</v>
+        <v>98323</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98323</v>
+        <v>98333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98333</v>
+        <v>98334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98334</v>
+        <v>98339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98341</v>
+        <v>98347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98347</v>
+        <v>98359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>98363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98363</v>
+        <v>98364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31444-2026 artfynd.xlsx
+++ b/artfynd/A 31444-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949694</v>
       </c>
       <c r="B2" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949696</v>
       </c>
       <c r="B3" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136950119</v>
       </c>
       <c r="B4" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136950117</v>
       </c>
       <c r="B5" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136950118</v>
       </c>
       <c r="B6" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136949695</v>
       </c>
       <c r="B13" t="n">
-        <v>98364</v>
+        <v>98367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
